--- a/output/pdf_financials_xlsx/GTWO.xlsx
+++ b/output/pdf_financials_xlsx/GTWO.xlsx
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000852</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-7e-06</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000911</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1074,13 +1074,13 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.124207</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.743331</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.370751</v>
       </c>
     </row>
     <row r="13">
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.136095</v>
+        <v>-7.135243</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.207762</v>
+        <v>0.207769</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.207215</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.770388</v>
+        <v>-0.769477</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.6002150000000001</v>
@@ -2053,13 +2053,13 @@
         <v>-2.203677</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.426451</v>
+        <v>-4.550658</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.098102</v>
+        <v>-3.841433</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-10.938514</v>
+        <v>-12.309265</v>
       </c>
     </row>
     <row r="28">
@@ -2144,16 +2144,16 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.085333</v>
+        <v>-7.084481</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.209137</v>
+        <v>0.209144</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.206195</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.770195</v>
+        <v>-0.769284</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.6002150000000001</v>
@@ -2171,13 +2171,13 @@
         <v>-2.151713</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.402781</v>
+        <v>-4.526988</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.085686</v>
+        <v>-3.829017</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-10.919255</v>
+        <v>-12.290006</v>
       </c>
     </row>
     <row r="30">
@@ -2447,10 +2447,10 @@
         <v>0.333533</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.165889</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.364834</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.312977</v>
@@ -2462,19 +2462,19 @@
         <v>0.583775</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.037445</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.252612</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>15.770755</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>16.65341</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>24.140797</v>
       </c>
     </row>
     <row r="35">
@@ -2561,10 +2561,10 @@
         <v>0.409909</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.061659</v>
+        <v>0.227548</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.06024</v>
+        <v>0.425074</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.331113</v>
@@ -2576,19 +2576,19 @@
         <v>0.588775</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>2.109445</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.06406299999999999</v>
+        <v>1.316675</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.05</v>
+        <v>15.820755</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.06</v>
+        <v>16.71341</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.2302</v>
+        <v>24.370997</v>
       </c>
     </row>
     <row r="37">
@@ -3245,10 +3245,10 @@
         <v>0.013115</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.174825</v>
+        <v>0.008935999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.381928</v>
+        <v>0.017094</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.012326</v>
@@ -3260,19 +3260,19 @@
         <v>0.049044</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.231469</v>
+        <v>0.194024</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.430969</v>
+        <v>0.178357</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>15.947321</v>
+        <v>0.176566</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>16.725273</v>
+        <v>0.071863</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>24.486697</v>
+        <v>0.3459</v>
       </c>
     </row>
     <row r="49">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -31522,7 +31522,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">

--- a/output/pdf_financials_xlsx/GTWO.xlsx
+++ b/output/pdf_financials_xlsx/GTWO.xlsx
@@ -18056,7 +18056,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -22036,7 +22040,11 @@
           <t>Private placements (note 10(b))</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -24156,7 +24164,11 @@
           <t>Private placements (note 6(b))</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -26658,7 +26670,11 @@
           <t>Private placement (note 7(b)(i))</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
